--- a/original_LATEST_COMPANY_AUDIT.xlsx
+++ b/original_LATEST_COMPANY_AUDIT.xlsx
@@ -1181,14 +1181,10 @@
           <t>https://www.linkedin.com/company/65411632/</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>http://linkedin.com/company/brandportunity</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>excluded_latest_company_has_website</t>
+          <t>kept_latest_company_no_website</t>
         </is>
       </c>
     </row>

--- a/original_LATEST_COMPANY_AUDIT.xlsx
+++ b/original_LATEST_COMPANY_AUDIT.xlsx
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AQUARIUS LOGISTICS AFRICA LTD</t>
+          <t>Aquarius Global Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1112,27 +1112,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EZRA Coaching</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/19114475/</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>http://www.helloezra.com</t>
-        </is>
-      </c>
+          <t>Consciously You LLC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>excluded_latest_company_has_website</t>
+          <t>kept_latest_company_no_page_url</t>
         </is>
       </c>
     </row>
